--- a/AAII_Financials/Yearly/VNET_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/VNET_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="92">
   <si>
     <t>VNET</t>
   </si>
@@ -1016,8 +1016,8 @@
       <c r="F14" s="3">
         <v>265400</v>
       </c>
-      <c r="G14" s="3">
-        <v>-3300</v>
+      <c r="G14" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="H14" s="3">
         <v>-112300</v>
@@ -1260,7 +1260,7 @@
         <v>32500</v>
       </c>
       <c r="G20" s="3">
-        <v>76900</v>
+        <v>73600</v>
       </c>
       <c r="H20" s="3">
         <v>-13000</v>
@@ -1311,7 +1311,7 @@
         <v>206000</v>
       </c>
       <c r="G21" s="3">
-        <v>172000</v>
+        <v>175300</v>
       </c>
       <c r="H21" s="3">
         <v>233500</v>
@@ -1872,7 +1872,7 @@
         <v>-32500</v>
       </c>
       <c r="G32" s="3">
-        <v>-76900</v>
+        <v>-73600</v>
       </c>
       <c r="H32" s="3">
         <v>13000</v>
